--- a/events/Shaoxing_2019_MAR/Shaoxing_2019_MAR_Results.xlsx
+++ b/events/Shaoxing_2019_MAR/Shaoxing_2019_MAR_Results.xlsx
@@ -31490,7 +31490,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Emily O’ROURKE</t>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>O’ROURKE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/events/Shaoxing_2019_MAR/Shaoxing_2019_MAR_Results.xlsx
+++ b/events/Shaoxing_2019_MAR/Shaoxing_2019_MAR_Results.xlsx
@@ -1140,6 +1140,11 @@
           <t>01:33:49.500</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2530,6 +2535,11 @@
           <t>01:31:49.560</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>77311</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3329,6 +3339,11 @@
           <t>01:46:51.160</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>83680</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7064,6 +7079,11 @@
           <t>00:18:41.180</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>103884</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9593,6 +9613,11 @@
           <t>00:19:43.050</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>97191</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14685,6 +14710,11 @@
           <t>01:24:24.710</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>104049</t>
+        </is>
+      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>104050</t>
@@ -14757,6 +14787,11 @@
           <t>94144</t>
         </is>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -14819,6 +14854,11 @@
           <t>01:25:45.570</t>
         </is>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>104039</t>
+        </is>
+      </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>104048</t>
@@ -15822,6 +15862,11 @@
           <t>01:26:50.280</t>
         </is>
       </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>77311</t>
+        </is>
+      </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>97578</t>
@@ -15894,6 +15939,11 @@
           <t>104057</t>
         </is>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>104061</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -17805,6 +17855,11 @@
           <t>01:57:06.170</t>
         </is>
       </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>104051</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -19495,6 +19550,11 @@
           <t>01:34:31.270</t>
         </is>
       </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>79270</t>
+        </is>
+      </c>
       <c r="S285" t="inlineStr">
         <is>
           <t>79271</t>
@@ -19706,6 +19766,11 @@
           <t>01:35:44.970</t>
         </is>
       </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>98038</t>
+        </is>
+      </c>
       <c r="S288" t="inlineStr">
         <is>
           <t>91294</t>
@@ -21833,6 +21898,11 @@
           <t>02:12:41.610</t>
         </is>
       </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>103884</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -26248,6 +26318,11 @@
           <t>02:09:45.320</t>
         </is>
       </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -27248,6 +27323,11 @@
           <t>02:18:58.500</t>
         </is>
       </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -28391,6 +28471,11 @@
           <t>58736</t>
         </is>
       </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>135293</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -30021,6 +30106,11 @@
           <t>01:58:49.190</t>
         </is>
       </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S441" t="inlineStr">
         <is>
           <t>64792</t>
@@ -30232,6 +30322,11 @@
           <t>01:59:53.670</t>
         </is>
       </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>87419</t>
+        </is>
+      </c>
       <c r="S444" t="inlineStr">
         <is>
           <t>87418</t>
@@ -30664,6 +30759,11 @@
           <t>70640</t>
         </is>
       </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>63429</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -31372,6 +31472,11 @@
       <c r="P460" t="inlineStr">
         <is>
           <t>02:29:58.910</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>103246</t>
         </is>
       </c>
       <c r="S460" t="inlineStr">
@@ -31457,7 +31562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D326"/>
+  <dimension ref="A1:D343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38632,6 +38737,380 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Joep</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>BAKEL VAN</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>63429</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Marton</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>MESZAROS</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>77311</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Benedek</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>HORVATH</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>79270</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Nestor Damian</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>PINTA</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>83680</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Jen-Hau</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>WU</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>87419</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>FERNANDEZ CASTANON</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>97191</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Ying</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>WANG</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>98038</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>CASTRO SILVA</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>103246</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Naocha Singh</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>LAITONJAM</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>103884</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Wei Jie Sean</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>TEO</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>104039</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Xiaowan</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ZHANG</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>104049</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Ningning</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>QU</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>104051</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Xiao</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>YANG</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>104061</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Jiadong</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>ZHU</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>130683</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Ardis</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>LUDA</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>135293</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Gergely</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>NAGY</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Shaoxing_2019_MAR/Shaoxing_2019_MAR_Results.xlsx
+++ b/events/Shaoxing_2019_MAR/Shaoxing_2019_MAR_Results.xlsx
@@ -3471,6 +3471,11 @@
           <t>00:16:42.740</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5459,6 +5464,11 @@
           <t>00:15:43.180</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>148720</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10618,6 +10628,11 @@
           <t>00:15:41.380</t>
         </is>
       </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -25003,6 +25018,11 @@
       <c r="P366" t="inlineStr">
         <is>
           <t>02:04:34.760</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>47779</t>
         </is>
       </c>
     </row>
@@ -31562,7 +31582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D343"/>
+  <dimension ref="A1:D345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39111,6 +39131,50 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>148720</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>ALGANARAS</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
